--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1360,7 +1360,11 @@
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-request-unique</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1528,7 +1528,11 @@
           <t>Leave Stage 3</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-clash</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1700,7 +1700,11 @@
           <t>Leave Stage 4</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-is-paid</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -907,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -980,15 +980,15 @@
           <t>STAGE 1 — WEEKLY OFF + BLACKOUT RULE</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1152,15 +1152,15 @@
           <t>STAGE 2 — LEAVEREQUEST MODEL</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1208,7 +1208,7 @@
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1261,6 +1261,11 @@
           <t>Leave Stage 2</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Declared on LeaveRequest.js — duplicate rejection verified in row 10.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1313,6 +1318,16 @@
           <t>Leave Stage 2</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Declared on LeaveRequest.js — leaveRequestSchema.index({ date: 1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> status: 1 }).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1372,15 +1387,15 @@
           <t>STAGE 3 — CLASH CHECKER</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1428,7 +1443,7 @@
           <t>Leave Stage 3</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n"/>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1481,6 +1496,16 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Leave Stage 3</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>excludeStaffId used only for swaps.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1540,15 +1565,15 @@
           <t>STAGE 4 — DEDUCTION CALCULATOR</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1653,6 +1678,7 @@
           <t>Leave Stage 4</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1712,15 +1738,15 @@
           <t>STAGE 5 — LEAVE SWAP</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1750,7 +1776,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1802,7 +1828,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1820,7 +1846,11 @@
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-swap</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1850,7 +1880,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1868,7 +1898,11 @@
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-swap-blackout</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1898,7 +1932,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1916,7 +1950,11 @@
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-swap-clash</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1924,15 +1962,15 @@
           <t>STAGE 6 — ATTENDANCE SYNC</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2084,7 +2122,7 @@
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n"/>
+      <c r="J27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2092,15 +2130,15 @@
           <t>STAGE 7 — LEAVE API ROUTES</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2148,7 +2186,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n"/>
+      <c r="J29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2196,7 +2234,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n"/>
+      <c r="J30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2244,7 +2282,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n"/>
+      <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2292,7 +2330,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n"/>
+      <c r="J32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2340,7 +2378,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n"/>
+      <c r="J33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2388,7 +2426,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n"/>
+      <c r="J34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2436,7 +2474,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n"/>
+      <c r="J35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2484,7 +2522,7 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n"/>
+      <c r="J36" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Patch models/Attendance.js.</t>
+          <t>npm run test:attendance-leave-request-id</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Call on every approval (and after swap creates approved rows).</t>
+          <t>npm run test:sync-attendance-for-leave</t>
         </is>
       </c>
     </row>

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -2104,7 +2104,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2122,7 +2122,11 @@
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:approve-leave-attendance</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2168,7 +2172,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2186,7 +2190,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>backend/routes/leaveRoutes.js — auth middleware; endpoints in rows 31–35.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2242,7 +2242,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Mounted at /api/leave via preciousRoutes.js</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -2276,7 +2276,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2294,7 +2294,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-request-api</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2346,7 +2346,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-approve-api</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2398,7 +2398,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-reject-api</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2428,7 +2432,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2446,7 +2450,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-swap-api</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2476,7 +2484,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -2494,7 +2502,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-list-api</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2524,7 +2536,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2542,7 +2554,11 @@
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:leave-happy-path</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -12,7 +12,12 @@
     <sheet name="02 Attendance-Holidays-Payroll" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="03 Frontend-UAT" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00 Overview'!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01 Leave-Clash-Swap'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 Attendance-Holidays-Payroll'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03 Frontend-UAT'!$A$1:$J$20</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -62,15 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -444,16 +446,16 @@
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,15 +516,15 @@
           <t>Leave + Holidays + Payroll — Implementation Tracker</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -530,15 +532,15 @@
           <t>Source: Leave-Clash-Swap-Implementation-Guide.docx + Attendance-Leave-Holidays-Payroll-Patch-Guide.docx | Heramb | August 2026</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -546,183 +548,183 @@
           <t>Build order is fixed — do not skip stages. Leave guide Stages 1-7 first; then Payroll patch Stages A-E; then frontend.</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Item Count</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Primary Owner</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>01 Leave-Clash-Swap</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>weekly_off_day, LeaveRequest, clash, is_paid, swap, Attendance sync, leave APIs</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>02 Attendance-Holidays-Payroll</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Holiday model, attendance summary patch, PayrollRun/Entry, payrollService, payroll+holiday APIs</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>03 Frontend-UAT</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Leave apply/approve/swap UI, holiday settings, payroll pages, MyEarnings, dry-run UAT</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>TOTAL TASKS</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -730,15 +732,15 @@
           <t>BUILD RULES</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -746,15 +748,15 @@
           <t>1. Implement Leave guide Stages 1-7 before any Payroll patch stage.</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -762,15 +764,15 @@
           <t>2. Test each stage (REPL/Postman) before moving to the next — match Flowgenix trace-before-fix.</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -778,15 +780,14 @@
           <t>3. Leave routes mount in preciousRoutes.js next to attendance (per Leave guide). Payroll mounts where payroll was planned (arnavRoutes.js).</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -794,15 +795,15 @@
           <t>4. Blackout rule lives in exactly one place: backend/constants/leaveConstants.js.</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -810,15 +811,15 @@
           <t>5. Fri/Sat/Sun overrides everything — never a valid off date.</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -826,15 +827,15 @@
           <t>6. Payroll is direct-pay only: base_salary - unpaid-day deduction + commission. No tax slabs.</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -842,27 +843,27 @@
           <t>7. Dry-run one employee one month by hand before trusting net_payable on real staff.</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -870,15 +871,15 @@
           <t>STATUS KEY</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -886,17 +887,18 @@
           <t>Not Started | In Progress | Blocked | Done | Verified</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -910,16 +912,16 @@
   <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -991,156 +993,156 @@
       <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>StaffProfile.weekly_off_day field</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Number 1=Mon..4=Thu; default 1; validator rejects 0/5/6 (Sun/Fri/Sat).</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 1</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Replace frontend-only Sunday weekly-off assumption.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>constants/leaveConstants.js</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>BLACKOUT_DAYS=[5,6,0]; ALLOWED_DAYS=[1,2,3,4]; isBlackoutDate(dateObj).</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 1</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Single source of truth — import everywhere.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Reject weekly_off_day=5; accept=2</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Model validator rejects Fri; accepts Tue.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 1</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Manual Compass/shell or seed script.</t>
         </is>
@@ -1163,219 +1165,219 @@
       <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>models/LeaveRequest.js</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>staff_id, date (UTC midnight), leave_type enum weekly_off|extra_leave|swapped_off, status pending|approved|rejected|cancelled, is_paid, swap_with_staff_id, reason, approved_by.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Unique index {staff_id</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> date}</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Mongo rejects second leave same staff same day.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Declared on LeaveRequest.js — duplicate rejection verified in row 10.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Index {date</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> status}</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Supports clash queries and calendar list.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Declared on LeaveRequest.js — leaveRequestSchema.index({ date: 1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> status: 1 }).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Insert one LeaveRequest; duplicate fails</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Unique index confirmed in Compass/shell.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-request-unique</t>
         </is>
@@ -1398,162 +1400,162 @@
       <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>services/leaveClashService.js — normalize()</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Normalize dates to UTC midnight for comparisons.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 3</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>checkClash({ staffId</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> date</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> excludeStaffId })</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1) blackout Fri/Sat/Sun → blocked; 2) same designation + approved leave same date → blocked; else allowed.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 3</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>excludeStaffId used only for swaps.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Beautician clash on Tuesday</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Second Beautician same Tue → allowed:false; Stylist same Tue → true; any Sat → false.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 3</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-clash</t>
         </is>
@@ -1576,157 +1578,157 @@
       <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>getWeekStart(date) Mon–Sun week</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>UTC Monday start of calendar week.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 4</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Add to leaveClashService.js.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>calculateIsPaid({ staffId</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> date })</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Count approved leaves same staff same week; first → paid true; 2nd+ → false.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2nd leave same week unpaid</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>1 approved this week → 2nd date same week is_paid false; next week true.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 4</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-is-paid</t>
         </is>
@@ -1749,208 +1751,208 @@
       <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>services/leaveSwapService.js — swapLeave()</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Check A→B date and B→A date via checkClash (with exclude); calculateIsPaid both; delete old; create swapped_off approved.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>No Mongo transaction in v1 — known gap.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Valid swap Mon↔Wed same designation free</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>success:true; both records swapped_off approved.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-swap</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Swap into blackout blocked</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Destination Fri/Sat/Sun → success:false; no writes.</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-swap-blackout</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Swap into designation clash blocked</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Target date already has same designation off → fail; no partial write.</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-swap-clash</t>
         </is>
@@ -1973,156 +1975,156 @@
       <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Attendance.leave_request_id field</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>ObjectId ref LeaveRequest; default null.</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>npm run test:attendance-leave-request-id</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>syncAttendanceForLeave(leaveRequest)</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Upsert Attendance by staff_id+date; status on_leave; remarks Paid/Unpaid leave; set leave_request_id.</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>npm run test:sync-attendance-for-leave</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Approve leave creates Attendance on_leave</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Attendance row exists with leave_request_id linked.</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>npm run test:approve-leave-attendance</t>
         </is>
@@ -2145,422 +2147,423 @@
       <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>routes/leaveRoutes.js created</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>New leave route module.</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>backend/routes/leaveRoutes.js — auth middleware; endpoints in rows 31–35.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Mount leaveRoutes in preciousRoutes.js</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Next to existing attendance routes per guide.</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Mounted at /api/leave via preciousRoutes.js</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>POST /api/leave/request</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Employee apply: checkClash + calculateIsPaid; save pending.</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-request-api</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>POST /api/leave/:id/approve</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Manager approve → approved + syncAttendanceForLeave.</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-approve-api</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>POST /api/leave/:id/reject</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Manager reject → rejected; no Attendance write.</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-reject-api</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>POST /api/leave/swap</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Calls swapLeave(); both land approved; sync Attendance both sides.</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-swap-api</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>GET /api/leave?staff_id=&amp;month=</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>List leave for staff / calendar view.</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-list-api</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Postman full leave happy path</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Request → approve → Attendance on_leave; clash reject; swap ok.</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>npm run test:leave-happy-path</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2571,19 +2574,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2644,65 +2647,65 @@
           <t>PREREQUISITE</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Leave Stages 1-7 complete</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>LeaveRequest + is_paid + Attendance on_leave sync working before Stage A.</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Payroll Gate</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Do not start Holidays/Payroll until Leave guide Done.</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:leave-stages-gate</t>
         </is>
       </c>
     </row>
@@ -2712,163 +2715,176 @@
           <t>STAGE A — HOLIDAY MODEL</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>models/Holiday.js</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>date (UTC midnight unique), name, branch_id null=all, is_active.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage A</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:holiday-model</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Index {date</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> branch_id}</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Supports month range queries.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage A</t>
         </is>
       </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:holiday-index</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Insert 2-3 holidays; duplicate date blocked</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Unique date index confirmed.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage A</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:holiday-unique</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2876,403 +2892,431 @@
           <t>STAGE B — ATTENDANCE SUMMARY PATCH</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Export getMonthlyAttendanceSummary helper</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Shared helper used by summary route + payrollService.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Patch attendanceRoutes.js (or extract service).</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-helper</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Populate leave_request_id on summary query</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>is_paid available without N+1 queries.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-leave-populate</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Holiday-aware day loop</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Holiday date skips present/leave/absent counting for that day.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-holiday-skip</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Count paid vs unpaid leave days</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>on_leave + leave_request_ref.is_paid → daysPaidLeave else daysUnpaidLeave.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-paid-leave</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>New payableDays formula</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>payableDays = present + late + half_day*0.5 + daysPaidLeave + holidayCount; unpaidDays = unpaidLeave + absent.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-payable-formula</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>workingDaysInMonth</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>totalDaysInMonth - holidayCount.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-working-days</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>GET /api/attendance/summary returns new fields</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>workingDaysInMonth, daysPaidLeave, daysUnpaidLeave, holidayCount, payableDays, unpaidDays.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-api-fields</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Hand-count one employee one month</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Seed holiday + paid leave + unpaid leave + presents; verify every returned field by hand.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:attendance-summary-hand-count</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3280,159 +3324,171 @@
           <t>STAGE C — PAYROLL MODELS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>models/PayrollRun.js</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>month, year, status draft|finalized, run_by, finalized_at; unique {month,year}.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage C</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-run-model</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>models/PayrollEntry.js</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>payroll_run_id, staff_id, base_salary, working_days_in_month, payable_days, unpaid_days, per_day_rate, deduction_amount, commission_total, net_payable; unique run+staff.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage C</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-entry-model</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Unique indexes for run and entry</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Duplicate month/year run fails; duplicate staff in run fails.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage C</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-unique</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3440,311 +3496,327 @@
           <t>STAGE D — PAYROLL SERVICE</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>services/payrollService.js — runPayrollForMonth()</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Upsert draft PayrollRun; for each active staff: summary → perDayRate → deduction → commission accrued → net_payable upsert entry; link commissions paid.</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Direct-pay only.</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-run-for-month</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Formula per_day_rate</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>base_salary / workingDaysInMonth (holidays excluded from denominator).</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-per-day-rate</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Formula deduction + net</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>deduction = round(perDay * unpaidDays); net = base - deduction + commission_total.</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-deduction-net</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Link CommissionEntry to run</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Set payroll_run_id + status paid so not double-counted next month.</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Field already on CommissionEntry — behavior patch only.</t>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-link-commissions</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>finalizePayrollRun(id)</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>status finalized + finalized_at; routes reject further calc unless reopen built.</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-finalize</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Upsert same month does not duplicate</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Second runPayrollForMonth updates same entries.</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-upsert</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3752,409 +3824,411 @@
           <t>STAGE E — PAYROLL + HOLIDAY ROUTES</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>routes/payrollRoutes.js</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>New payroll API module.</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n"/>
+      <c r="J29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Mount payroll routes (arnavRoutes)</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Where payroll was already commented as planned.</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Confirm mount file vs Leave's preciousRoutes.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>POST /api/payroll/run</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Body {month</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>year}; creates/updates draft run + entries.</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
+      <c r="K31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>GET /api/payroll/run/:id</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Run + entries populated with staff name/designation.</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n"/>
+      <c r="J32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>POST /api/payroll/run/:id/finalize</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Locks the run.</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n"/>
+      <c r="J33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>GET /api/payroll/staff/:staffId?month=&amp;year=</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Employee payslip for MyEarnings.</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n"/>
+      <c r="J34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>GET /api/holidays?month=&amp;year=</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>List holidays for month — feeds summary + settings UI.</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n"/>
+      <c r="J35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>POST /api/holidays</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Admin adds holiday date.</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n"/>
+      <c r="J36" s="3" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4168,16 +4242,16 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4238,311 +4312,311 @@
           <t>LEAVE FRONTEND</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Employee apply-leave form</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Pick date Mon-Thu; leave_type; reason; call POST /api/leave/request; show clash errors.</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Desktop and/or mobile PWA — confirm UX with lead.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Manager approval screen</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>List pending; approve/reject; show designation clash context.</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n"/>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Leave swap UI</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Select peer + dates; call POST /api/leave/swap; surface failure reasons.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Staff weekly_off_day in Employees form</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Owner sets Mon-Thu weekly off on Staff Master (alongside salary/targets).</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n"/>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Remove hardcoded Sunday weekly-off</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Replace isWeeklyOffDay Sunday assumption with StaffProfile.weekly_off_day.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>attendanceUtils.js + mobile attendance history.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Mobile leave history (optional polish)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Show approved/pending leaves on mobile Attendance alongside punch history.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Extends earlier mobile attendance work.</t>
         </is>
@@ -4554,215 +4628,215 @@
           <t>HOLIDAY + PAYROLL FRONTEND</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Holiday settings screen</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Admin CRUD list of holidays (name + date); uses GET/POST /api/holidays.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Settings area.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Wire PayrollHome / RunPayroll placeholders</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Generate draft run; list entries; finalize.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>pages/payroll/* already stubbed.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>MyEarnings.jsx payslip</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Point at GET /api/payroll/staff/:staffId?month=&amp;year=.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n"/>
+      <c r="J12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Mobile earnings shows net if needed</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Align mobile Earnings with payslip fields when API ready.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4770,309 +4844,310 @@
           <t>UAT / DRY-RUN</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Leave blackout never allows Fri-Sun</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>All leave/swap paths return blocked.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n"/>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Designation clash blocks same-day offs</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Two Beauticians cannot both be approved off same Mon-Thu date.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n"/>
+      <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>1st weekly off paid; 2nd unpaid</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Attendance remarks + is_paid + payroll unpaidDays agree.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Holiday excluded from working days</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>payableDays includes holidayCount; denominator excludes holiday.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Hand-calc net_payable one employee one month</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Manually compute base - deduction + commission; match PayrollEntry before real staff run.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Required by Payroll guide §8.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Mark tracker rows Done → Verified</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Update Status column after each stage test passes.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n"/>
+      <c r="J20" s="3" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Leave-Payroll-Implementation-Tracker.xlsx
+++ b/Leave-Payroll-Implementation-Tracker.xlsx
@@ -67,12 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -447,15 +448,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,172 +560,172 @@
       <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Item Count</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Primary Owner</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>01 Leave-Clash-Swap</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>weekly_off_day, LeaveRequest, clash, is_paid, swap, Attendance sync, leave APIs</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>02 Attendance-Holidays-Payroll</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Holiday model, attendance summary patch, PayrollRun/Entry, payrollService, payroll+holiday APIs</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>03 Frontend-UAT</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Leave apply/approve/swap UI, holiday settings, payroll pages, MyEarnings, dry-run UAT</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TOTAL TASKS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -788,6 +789,7 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -854,16 +856,16 @@
       <c r="J20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -909,19 +911,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,156 +995,156 @@
       <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>StaffProfile.weekly_off_day field</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Number 1=Mon..4=Thu; default 1; validator rejects 0/5/6 (Sun/Fri/Sat).</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 1</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Replace frontend-only Sunday weekly-off assumption.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>constants/leaveConstants.js</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>BLACKOUT_DAYS=[5,6,0]; ALLOWED_DAYS=[1,2,3,4]; isBlackoutDate(dateObj).</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 1</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Single source of truth — import everywhere.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Reject weekly_off_day=5; accept=2</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Model validator rejects Fri; accepts Tue.</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 1</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Manual Compass/shell or seed script.</t>
         </is>
@@ -1165,219 +1167,204 @@
       <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>models/LeaveRequest.js</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>staff_id, date (UTC midnight), leave_type enum weekly_off|extra_leave|swapped_off, status pending|approved|rejected|cancelled, is_paid, swap_with_staff_id, reason, approved_by.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Unique index {staff_id</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> date}</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Mongo rejects second leave same staff same day.</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Declared on LeaveRequest.js — duplicate rejection verified in row 10.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Index {date</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> status}</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Supports clash queries and calendar list.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Declared on LeaveRequest.js — leaveRequestSchema.index({ date: 1</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> status: 1 }).</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Insert one LeaveRequest; duplicate fails</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Unique index confirmed in Compass/shell.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 2</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-request-unique</t>
         </is>
@@ -1400,162 +1387,152 @@
       <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>services/leaveClashService.js — normalize()</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Normalize dates to UTC midnight for comparisons.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 3</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>checkClash({ staffId</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> date</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> excludeStaffId })</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>1) blackout Fri/Sat/Sun → blocked; 2) same designation + approved leave same date → blocked; else allowed.</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Beautician clash on Tuesday</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Second Beautician same Tue → allowed:false; Stylist same Tue → true; any Sat → false.</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 3</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>excludeStaffId used only for swaps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Leave</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Beautician clash on Tuesday</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Second Beautician same Tue → allowed:false; Stylist same Tue → true; any Sat → false.</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Leave Stage 3</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-clash</t>
         </is>
@@ -1578,157 +1555,156 @@
       <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>getWeekStart(date) Mon–Sun week</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>UTC Monday start of calendar week.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 4</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Add to leaveClashService.js.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>calculateIsPaid({ staffId</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> date })</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Count approved leaves same staff same week; first → paid true; 2nd+ → false.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 4</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>2nd leave same week unpaid</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>1 approved this week → 2nd date same week is_paid false; next week true.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 4</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-is-paid</t>
         </is>
@@ -1751,208 +1727,208 @@
       <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>services/leaveSwapService.js — swapLeave()</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Check A→B date and B→A date via checkClash (with exclude); calculateIsPaid both; delete old; create swapped_off approved.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>No Mongo transaction in v1 — known gap.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Valid swap Mon↔Wed same designation free</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>success:true; both records swapped_off approved.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-swap</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Swap into blackout blocked</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Destination Fri/Sat/Sun → success:false; no writes.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-swap-blackout</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Swap into designation clash blocked</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Target date already has same designation off → fail; no partial write.</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 5</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-swap-clash</t>
         </is>
@@ -1975,156 +1951,156 @@
       <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Attendance.leave_request_id field</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>ObjectId ref LeaveRequest; default null.</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-leave-request-id</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>syncAttendanceForLeave(leaveRequest)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Upsert Attendance by staff_id+date; status on_leave; remarks Paid/Unpaid leave; set leave_request_id.</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>npm run test:sync-attendance-for-leave</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Approve leave creates Attendance on_leave</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Attendance row exists with leave_request_id linked.</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 6</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>npm run test:approve-leave-attendance</t>
         </is>
@@ -2147,416 +2123,416 @@
       <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>routes/leaveRoutes.js created</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>New leave route module.</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>backend/routes/leaveRoutes.js — auth middleware; endpoints in rows 31–35.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Mount leaveRoutes in preciousRoutes.js</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Next to existing attendance routes per guide.</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Mounted at /api/leave via preciousRoutes.js</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>POST /api/leave/request</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Employee apply: checkClash + calculateIsPaid; save pending.</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-request-api</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>POST /api/leave/:id/approve</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Manager approve → approved + syncAttendanceForLeave.</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-approve-api</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>POST /api/leave/:id/reject</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Manager reject → rejected; no Attendance write.</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-reject-api</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>POST /api/leave/swap</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Calls swapLeave(); both land approved; sync Attendance both sides.</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-swap-api</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>GET /api/leave?staff_id=&amp;month=</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>List leave for staff / calendar view.</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-list-api</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Postman full leave happy path</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Request → approve → Attendance on_leave; clash reject; swap ok.</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Leave Stage 7</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-happy-path</t>
         </is>
@@ -2574,19 +2550,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2658,52 +2634,52 @@
       <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Leave Stages 1-7 complete</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>LeaveRequest + is_paid + Attendance on_leave sync working before Stage A.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Payroll Gate</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>npm run test:leave-stages-gate</t>
         </is>
@@ -2726,161 +2702,156 @@
       <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>models/Holiday.js</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>date (UTC midnight unique), name, branch_id null=all, is_active.</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage A</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>npm run test:holiday-model</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Index {date</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> branch_id}</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Supports month range queries.</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage A</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>npm run test:holiday-index</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Insert 2-3 holidays; duplicate date blocked</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Unique date index confirmed.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage A</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>npm run test:holiday-unique</t>
         </is>
@@ -2903,416 +2874,416 @@
       <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Export getMonthlyAttendanceSummary helper</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Shared helper used by summary route + payrollService.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-helper</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Populate leave_request_id on summary query</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>is_paid available without N+1 queries.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-leave-populate</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Holiday-aware day loop</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Holiday date skips present/leave/absent counting for that day.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-holiday-skip</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Count paid vs unpaid leave days</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>on_leave + leave_request_ref.is_paid → daysPaidLeave else daysUnpaidLeave.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-paid-leave</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>New payableDays formula</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>payableDays = present + late + half_day*0.5 + daysPaidLeave + holidayCount; unpaidDays = unpaidLeave + absent.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-payable-formula</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>workingDaysInMonth</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>totalDaysInMonth - holidayCount.</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-working-days</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>GET /api/attendance/summary returns new fields</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>workingDaysInMonth, daysPaidLeave, daysUnpaidLeave, holidayCount, payableDays, unpaidDays.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-api-fields</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Hand-count one employee one month</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Seed holiday + paid leave + unpaid leave + presents; verify every returned field by hand.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage B</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>npm run test:attendance-summary-hand-count</t>
         </is>
@@ -3335,156 +3306,156 @@
       <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>models/PayrollRun.js</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>month, year, status draft|finalized, run_by, finalized_at; unique {month,year}.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage C</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-run-model</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>models/PayrollEntry.js</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>payroll_run_id, staff_id, base_salary, working_days_in_month, payable_days, unpaid_days, per_day_rate, deduction_amount, commission_total, net_payable; unique run+staff.</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage C</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-entry-model</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Unique indexes for run and entry</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Duplicate month/year run fails; duplicate staff in run fails.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage C</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-unique</t>
         </is>
@@ -3507,312 +3478,312 @@
       <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>services/payrollService.js — runPayrollForMonth()</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Upsert draft PayrollRun; for each active staff: summary → perDayRate → deduction → commission accrued → net_payable upsert entry; link commissions paid.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-run-for-month</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Formula per_day_rate</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>base_salary / workingDaysInMonth (holidays excluded from denominator).</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-per-day-rate</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Formula deduction + net</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>deduction = round(perDay * unpaidDays); net = base - deduction + commission_total.</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-deduction-net</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Link CommissionEntry to run</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Set payroll_run_id + status paid so not double-counted next month.</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-link-commissions</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>finalizePayrollRun(id)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>status finalized + finalized_at; routes reject further calc unless reopen built.</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-finalize</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Upsert same month does not duplicate</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Second runPayrollForMonth updates same entries.</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage D</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>npm run test:payroll-upsert</t>
         </is>
@@ -3835,397 +3806,420 @@
       <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>routes/payrollRoutes.js</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>New payroll API module.</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-routes-module; auth + endpoints declared; mount is row 30.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Mount payroll routes (arnavRoutes)</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Where payroll was already commented as planned.</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Confirm mount file vs Leave's preciousRoutes.</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-routes-mount; mounted at /api/payroll via arnavRoutes (Leave stays on preciousRoutes).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>POST /api/payroll/run</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Body {month</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>year}; creates/updates draft run + entries.</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Body {month,year}; creates/updates draft run + entries.</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-run-api</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>GET /api/payroll/run/:id</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Run + entries populated with staff name/designation.</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-get-run-api</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>POST /api/payroll/run/:id/finalize</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Locks the run.</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-finalize-api</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>GET /api/payroll/staff/:staffId?month=&amp;year=</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Employee payslip for MyEarnings.</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:payroll-staff-payslip-api</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>GET /api/holidays?month=&amp;year=</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>List holidays for month — feeds summary + settings UI.</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:holiday-list-api</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>POST /api/holidays</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Admin adds holiday date.</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Payroll Stage E</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:holiday-create-api</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J36"/>
@@ -4243,15 +4237,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4323,302 +4317,314 @@
       <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Employee apply-leave form</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Pick date Mon-Thu; leave_type; reason; call POST /api/leave/request; show clash errors.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Desktop and/or mobile PWA — confirm UX with lead.</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Desktop Attendance tab + mobile Attendance form.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Manager approval screen</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>List pending; approve/reject; show designation clash context.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Desktop Attendance tab; GET /api/leave?status=pending + clash context.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Leave swap UI</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Select peer + dates; call POST /api/leave/swap; surface failure reasons.</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Desktop Attendance tab.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Staff weekly_off_day in Employees form</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Owner sets Mon-Thu weekly off on Staff Master (alongside salary/targets).</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Employees / Staff Master form; POST/PUT /api/staff persist weekly_off_day.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Remove hardcoded Sunday weekly-off</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Replace isWeeklyOffDay Sunday assumption with StaffProfile.weekly_off_day.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>attendanceUtils.js + mobile attendance history.</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>attendanceUtils.js + mobile attendance history use weekly_off_day.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Mobile leave history (optional polish)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Show approved/pending leaves on mobile Attendance alongside punch history.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Extends earlier mobile attendance work.</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Week list + last 14 days history include pending/approved leave.</t>
         </is>
       </c>
     </row>
@@ -4639,204 +4645,212 @@
       <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Holiday settings screen</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Admin CRUD list of holidays (name + date); uses GET/POST /api/holidays.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Settings area.</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Settings /settings/holidays; list+add only (GET/POST).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Wire PayrollHome / RunPayroll placeholders</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Generate draft run; list entries; finalize.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>pages/payroll/* already stubbed.</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>PayrollHome hub + /payroll/run POST/GET/finalize.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>MyEarnings.jsx payslip</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Point at GET /api/payroll/staff/:staffId?month=&amp;year=.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Desktop My earnings shows net payable from payslip API.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Mobile earnings shows net if needed</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Align mobile Earnings with payslip fields when API ready.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Mobile Earnings shows net/deduction from payslip API.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4855,296 +4869,316 @@
       <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Leave blackout never allows Fri-Sun</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>All leave/swap paths return blocked.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:uat-leave-blackout — Fri/Sat/Sun blocked on clash request and swap.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Designation clash blocks same-day offs</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Two Beauticians cannot both be approved off same Mon-Thu date.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:uat-leave-designation-clash — request/approve/swap; approve re-checks clash.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>1st weekly off paid; 2nd unpaid</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Attendance remarks + is_paid + payroll unpaidDays agree.</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:uat-paid-unpaid-weekly-off — Paid/Unpaid remarks match unpaid_days=1.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Holiday excluded from working days</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>payableDays includes holidayCount; denominator excludes holiday.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:uat-holiday-working-days — payable includes holidays; per-day uses 30-2=28.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Hand-calc net_payable one employee one month</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Manually compute base - deduction + commission; match PayrollEntry before real staff run.</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>Required by Payroll guide §8.</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>npm run test:uat-hand-calc-net — 25000-893+1750=25857 matches PayrollEntry.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Mark tracker rows Done → Verified</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Update Status column after each stage test passes.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Arnav</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Arnav</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Sheet 01 leftover Done promoted (stage tests passed). Sheet 02 already Verified. Sheet 03 frontend stays Done (UX shipped; APIs covered by UAT 15-19).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J20"/>
